--- a/data/trans_camb/IP18A02-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP18A02-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,85; 6,58</t>
+          <t>-11,24; 6,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-14,3; 2,67</t>
+          <t>-14,7; 2,84</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-16,04; 22,72</t>
+          <t>-17,29; 19,49</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,76; 5,18</t>
+          <t>-11,17; 5,91</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-14,6; 1,68</t>
+          <t>-13,8; 2,69</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-22,01; 2,0</t>
+          <t>-22,24; 0,55</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-8,13; 3,96</t>
+          <t>-8,94; 3,93</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-12,31; -0,76</t>
+          <t>-11,98; 0,41</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-16,41; 4,63</t>
+          <t>-17,48; 2,64</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-40,04; 34,03</t>
+          <t>-39,47; 32,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-50,23; 17,78</t>
+          <t>-53,34; 14,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-62,75; 110,88</t>
+          <t>-67,65; 95,02</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-39,55; 29,2</t>
+          <t>-41,7; 31,23</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-54,23; 8,37</t>
+          <t>-51,68; 15,85</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-88,38; 19,59</t>
+          <t>-89,36; 7,26</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-31,72; 19,91</t>
+          <t>-33,22; 19,85</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-46,45; -3,59</t>
+          <t>-45,55; 2,1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-66,25; 26,85</t>
+          <t>-69,58; 11,54</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,13; 5,93</t>
+          <t>-7,52; 5,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,74; 6,9</t>
+          <t>-5,97; 7,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,62; 17,55</t>
+          <t>-9,41; 18,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-12,62; 0,82</t>
+          <t>-12,23; 0,39</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-9,2; 3,55</t>
+          <t>-9,56; 3,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,78; 16,85</t>
+          <t>-5,94; 18,38</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-7,88; 1,25</t>
+          <t>-8,04; 1,16</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-6,76; 2,83</t>
+          <t>-5,9; 3,16</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 13,14</t>
+          <t>-4,53; 12,71</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-34,43; 39,95</t>
+          <t>-33,34; 33,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-26,45; 47,01</t>
+          <t>-28,67; 46,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-52,26; 110,41</t>
+          <t>-49,64; 105,9</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-51,25; 6,0</t>
+          <t>-50,52; 3,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-38,44; 21,27</t>
+          <t>-39,68; 20,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-24,83; 92,3</t>
+          <t>-27,46; 96,19</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-36,27; 7,35</t>
+          <t>-36,26; 8,02</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-30,29; 15,98</t>
+          <t>-26,27; 19,09</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-18,31; 70,22</t>
+          <t>-21,81; 69,11</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-13,32; 2,15</t>
+          <t>-13,23; 2,72</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,78; 2,03</t>
+          <t>-13,29; 2,53</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-15,31; 13,34</t>
+          <t>-17,05; 13,08</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,53; 9,07</t>
+          <t>-6,56; 8,55</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 13,96</t>
+          <t>-2,13; 13,24</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-15,48; 11,48</t>
+          <t>-14,46; 12,27</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-7,54; 3,69</t>
+          <t>-7,55; 3,57</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,19; 6,02</t>
+          <t>-5,84; 5,55</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-13,05; 6,56</t>
+          <t>-12,84; 7,17</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-46,3; 10,75</t>
+          <t>-47,15; 13,65</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-45,37; 11,8</t>
+          <t>-46,38; 12,75</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-60,17; 63,78</t>
+          <t>-62,89; 58,6</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-28,26; 61,46</t>
+          <t>-27,86; 61,75</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-12,98; 90,81</t>
+          <t>-9,36; 88,22</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-72,72; 77,5</t>
+          <t>-71,82; 78,85</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-29,63; 20,48</t>
+          <t>-30,61; 18,6</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-20,79; 32,6</t>
+          <t>-24,1; 29,45</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-55,56; 34,64</t>
+          <t>-54,7; 33,8</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,52; 6,31</t>
+          <t>-8,41; 6,79</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-14,13; 0,61</t>
+          <t>-13,3; 0,91</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-22,76; 1,06</t>
+          <t>-23,13; 0,65</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 9,37</t>
+          <t>-4,41; 9,34</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,59; 7,88</t>
+          <t>-5,84; 7,31</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-10,92; 16,61</t>
+          <t>-11,86; 13,37</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 5,53</t>
+          <t>-5,0; 5,72</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-8,04; 1,35</t>
+          <t>-8,12; 1,79</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-14,14; 3,39</t>
+          <t>-13,77; 3,57</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-28,38; 27,73</t>
+          <t>-28,03; 29,57</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-46,71; 2,59</t>
+          <t>-44,28; 3,78</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-80,81; 6,14</t>
+          <t>-82,67; 5,41</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-19,1; 60,57</t>
+          <t>-19,01; 63,15</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-26,42; 50,56</t>
+          <t>-27,04; 48,79</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-54,62; 98,15</t>
+          <t>-57,44; 76,68</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-17,31; 27,47</t>
+          <t>-19,37; 28,19</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-31,64; 6,85</t>
+          <t>-31,37; 10,3</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-59,74; 17,95</t>
+          <t>-57,16; 15,83</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,21; 1,51</t>
+          <t>-6,34; 1,68</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-8,2; -0,95</t>
+          <t>-8,35; -0,78</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-10,89; 3,36</t>
+          <t>-10,55; 3,27</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 2,19</t>
+          <t>-5,35; 2,12</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 2,68</t>
+          <t>-4,39; 2,67</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-6,64; 5,89</t>
+          <t>-6,73; 5,55</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 0,84</t>
+          <t>-4,51; 1,12</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 0,02</t>
+          <t>-5,04; 0,19</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-6,99; 2,2</t>
+          <t>-7,02; 2,15</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-24,46; 7,67</t>
+          <t>-24,08; 8,58</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-32,55; -4,29</t>
+          <t>-32,78; -3,46</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-45,47; 14,95</t>
+          <t>-43,12; 14,82</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-21,79; 12,28</t>
+          <t>-24,57; 11,46</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-21,19; 14,48</t>
+          <t>-20,25; 14,37</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-31,71; 30,88</t>
+          <t>-31,11; 29,31</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-18,57; 3,98</t>
+          <t>-19,19; 5,45</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-21,49; 0,11</t>
+          <t>-21,51; 1,04</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-31,14; 10,65</t>
+          <t>-31,52; 10,05</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP18A02-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP18A02-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,24; 6,47</t>
+          <t>-10,38; 6,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-14,7; 2,84</t>
+          <t>-15,02; 2,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-17,29; 19,49</t>
+          <t>-17,56; 18,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,17; 5,91</t>
+          <t>-10,8; 4,72</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-13,8; 2,69</t>
+          <t>-15,34; 1,63</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-22,24; 0,55</t>
+          <t>-21,72; 1,4</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-8,94; 3,93</t>
+          <t>-8,3; 3,25</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-11,98; 0,41</t>
+          <t>-12,16; -0,12</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-17,48; 2,64</t>
+          <t>-16,56; 3,8</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-39,47; 32,62</t>
+          <t>-37,06; 33,98</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-53,34; 14,44</t>
+          <t>-52,78; 17,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-67,65; 95,02</t>
+          <t>-68,16; 88,02</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-41,7; 31,23</t>
+          <t>-40,47; 27,89</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-51,68; 15,85</t>
+          <t>-56,34; 10,2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-89,36; 7,26</t>
+          <t>-90,31; 9,99</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-33,22; 19,85</t>
+          <t>-32,42; 15,88</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-45,55; 2,1</t>
+          <t>-45,45; -0,0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-69,58; 11,54</t>
+          <t>-66,21; 19,38</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,52; 5,16</t>
+          <t>-6,78; 5,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,97; 7,11</t>
+          <t>-5,79; 6,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,41; 18,35</t>
+          <t>-9,59; 17,96</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-12,23; 0,39</t>
+          <t>-12,47; 0,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-9,56; 3,39</t>
+          <t>-9,47; 3,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,94; 18,38</t>
+          <t>-6,35; 16,96</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-8,04; 1,16</t>
+          <t>-7,87; 0,8</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 3,16</t>
+          <t>-6,13; 2,8</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 12,71</t>
+          <t>-3,87; 13,46</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-33,34; 33,85</t>
+          <t>-32,24; 38,72</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-28,67; 46,77</t>
+          <t>-26,04; 46,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-49,64; 105,9</t>
+          <t>-47,31; 105,88</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-50,52; 3,85</t>
+          <t>-50,85; 2,95</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-39,68; 20,76</t>
+          <t>-38,44; 19,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-27,46; 96,19</t>
+          <t>-27,49; 92,33</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-36,26; 8,02</t>
+          <t>-36,05; 4,75</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-26,27; 19,09</t>
+          <t>-27,35; 16,41</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-21,81; 69,11</t>
+          <t>-19,9; 73,16</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-13,23; 2,72</t>
+          <t>-13,65; 2,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-13,29; 2,53</t>
+          <t>-13,09; 2,58</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-17,05; 13,08</t>
+          <t>-16,87; 13,36</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,56; 8,55</t>
+          <t>-6,8; 8,01</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 13,24</t>
+          <t>-2,04; 13,65</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-14,46; 12,27</t>
+          <t>-14,7; 10,58</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-7,55; 3,57</t>
+          <t>-7,51; 3,23</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,84; 5,55</t>
+          <t>-5,27; 6,47</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-12,84; 7,17</t>
+          <t>-12,74; 7,24</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-47,15; 13,65</t>
+          <t>-45,82; 15,52</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-46,38; 12,75</t>
+          <t>-45,86; 13,48</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-62,89; 58,6</t>
+          <t>-61,26; 55,35</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-27,86; 61,75</t>
+          <t>-29,94; 53,94</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-9,36; 88,22</t>
+          <t>-10,79; 89,44</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-71,82; 78,85</t>
+          <t>-69,21; 70,53</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-30,61; 18,6</t>
+          <t>-30,99; 16,81</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-24,1; 29,45</t>
+          <t>-21,55; 34,33</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-54,7; 33,8</t>
+          <t>-53,13; 38,89</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,41; 6,79</t>
+          <t>-8,15; 6,61</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-13,3; 0,91</t>
+          <t>-13,8; 0,55</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-23,13; 0,65</t>
+          <t>-22,13; 0,94</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 9,34</t>
+          <t>-4,15; 9,35</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,84; 7,31</t>
+          <t>-5,91; 7,24</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-11,86; 13,37</t>
+          <t>-12,93; 13,48</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 5,72</t>
+          <t>-4,82; 5,39</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-8,12; 1,79</t>
+          <t>-7,86; 1,93</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-13,77; 3,57</t>
+          <t>-13,63; 3,58</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-28,03; 29,57</t>
+          <t>-27,76; 27,89</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-44,28; 3,78</t>
+          <t>-45,36; 4,59</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-82,67; 5,41</t>
+          <t>-79,91; 4,12</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-19,01; 63,15</t>
+          <t>-19,12; 59,67</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-27,04; 48,79</t>
+          <t>-27,97; 46,27</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-57,44; 76,68</t>
+          <t>-56,17; 78,06</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-19,37; 28,19</t>
+          <t>-18,92; 26,03</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-31,37; 10,3</t>
+          <t>-32,42; 8,28</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-57,16; 15,83</t>
+          <t>-56,4; 17,3</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,34; 1,68</t>
+          <t>-6,25; 1,58</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-8,35; -0,78</t>
+          <t>-7,93; 0,02</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-10,55; 3,27</t>
+          <t>-10,27; 3,55</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-5,35; 2,12</t>
+          <t>-4,87; 2,36</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 2,67</t>
+          <t>-4,45; 2,75</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-6,73; 5,55</t>
+          <t>-6,78; 5,75</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 1,12</t>
+          <t>-4,4; 0,52</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 0,19</t>
+          <t>-4,85; 0,34</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-7,02; 2,15</t>
+          <t>-7,78; 1,91</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-24,08; 8,58</t>
+          <t>-25,09; 7,44</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-32,78; -3,46</t>
+          <t>-31,69; -0,26</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-43,12; 14,82</t>
+          <t>-42,69; 15,6</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-24,57; 11,46</t>
+          <t>-22,08; 12,6</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-20,25; 14,37</t>
+          <t>-20,22; 14,85</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-31,11; 29,31</t>
+          <t>-31,79; 30,46</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-19,19; 5,45</t>
+          <t>-19,19; 2,61</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-21,51; 1,04</t>
+          <t>-20,92; 1,99</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-31,52; 10,05</t>
+          <t>-35,08; 9,53</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP18A02-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP18A02-Habitat-trans_camb.xlsx
@@ -523,20 +523,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por control de salud periódico</t>
+          <t>Menores cuya última consulta médica fue por control de salud periódico</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-2,66</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-6,08</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-12,48</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-2,16</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-6,04</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-1,99</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-2,66</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-6,08</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-12,43</t>
+          <t>-2,87</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-7,87</t>
+          <t>-8,06</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,38; 6,47</t>
+          <t>-10,76; 5,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-15,02; 2,99</t>
+          <t>-14,6; 1,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-17,56; 18,92</t>
+          <t>-21,99; 2,53</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,8; 4,72</t>
+          <t>-10,85; 6,58</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-15,34; 1,63</t>
+          <t>-14,3; 2,67</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-21,72; 1,4</t>
+          <t>-16,51; 21,85</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-8,3; 3,25</t>
+          <t>-8,13; 3,96</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-12,16; -0,12</t>
+          <t>-12,31; -0,76</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-16,56; 3,8</t>
+          <t>-16,49; 4,93</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-11,77%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-26,94%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-55,25%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-8,99%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-25,19%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-8,29%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-11,77%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-26,94%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-55,02%</t>
+          <t>-11,96%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-33,87%</t>
+          <t>-34,69%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-37,06; 33,98</t>
+          <t>-39,55; 29,2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-52,78; 17,1</t>
+          <t>-54,23; 8,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-68,16; 88,02</t>
+          <t>-87,35; 22,22</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-40,47; 27,89</t>
+          <t>-40,04; 34,03</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-56,34; 10,2</t>
+          <t>-50,23; 17,78</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-90,31; 9,99</t>
+          <t>-64,54; 108,66</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-32,42; 15,88</t>
+          <t>-31,72; 19,91</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-45,45; -0,0</t>
+          <t>-46,45; -3,59</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-66,21; 19,38</t>
+          <t>-67,15; 28,66</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-5,95</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-3,14</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>6,03</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-0,85</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0,38</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1,63</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-5,95</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-3,14</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,98</t>
+          <t>4,22</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>4,02</t>
+          <t>5,62</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,78; 5,59</t>
+          <t>-12,62; 0,82</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,79; 6,75</t>
+          <t>-9,2; 3,55</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,59; 17,96</t>
+          <t>-4,92; 19,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-12,47; 0,36</t>
+          <t>-7,13; 5,93</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-9,47; 3,42</t>
+          <t>-5,74; 6,9</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,35; 16,96</t>
+          <t>-8,64; 23,18</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-7,87; 0,8</t>
+          <t>-7,88; 1,25</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-6,13; 2,8</t>
+          <t>-6,76; 2,83</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 13,46</t>
+          <t>-2,65; 15,7</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-28,53%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-15,06%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>28,93%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-4,64%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>2,05%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>8,85%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-28,53%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-15,06%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>28,59%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-32,24; 38,72</t>
+          <t>-51,25; 6,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-26,04; 46,04</t>
+          <t>-38,44; 21,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-47,31; 105,88</t>
+          <t>-22,41; 103,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-50,85; 2,95</t>
+          <t>-34,43; 39,95</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-38,44; 19,76</t>
+          <t>-26,45; 47,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-27,49; 92,33</t>
+          <t>-43,64; 138,42</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-36,05; 4,75</t>
+          <t>-36,27; 7,35</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-27,35; 16,41</t>
+          <t>-30,29; 15,98</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-19,9; 73,16</t>
+          <t>-13,6; 83,23</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>1,09</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>5,97</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-4,52</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-5,44</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-5,49</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-3,19</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,09</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>5,97</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-4,65</t>
+          <t>-1,08</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-4,16</t>
+          <t>-3,25</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-13,65; 2,99</t>
+          <t>-6,53; 9,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-13,09; 2,58</t>
+          <t>-2,69; 13,96</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-16,87; 13,36</t>
+          <t>-15,38; 12,48</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,8; 8,01</t>
+          <t>-13,32; 2,15</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 13,65</t>
+          <t>-12,78; 2,03</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-14,7; 10,58</t>
+          <t>-13,53; 17,35</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-7,51; 3,23</t>
+          <t>-7,54; 3,69</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,27; 6,47</t>
+          <t>-5,19; 6,02</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-12,74; 7,24</t>
+          <t>-12,24; 8,66</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>5,72%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>31,37%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-23,77%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-22,03%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-22,25%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-12,94%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>5,72%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>31,37%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-24,45%</t>
+          <t>-4,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-19,11%</t>
+          <t>-14,92%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-45,82; 15,52</t>
+          <t>-28,26; 61,46</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-45,86; 13,48</t>
+          <t>-12,98; 90,81</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-61,26; 55,35</t>
+          <t>-73,24; 80,65</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-29,94; 53,94</t>
+          <t>-46,3; 10,75</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-10,79; 89,44</t>
+          <t>-45,37; 11,8</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-69,21; 70,53</t>
+          <t>-52,45; 74,69</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-30,99; 16,81</t>
+          <t>-29,63; 20,48</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-21,55; 34,33</t>
+          <t>-20,79; 32,6</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-53,13; 38,89</t>
+          <t>-52,48; 42,03</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2,27</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0,66</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-0,02</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-1,13</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-6,42</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-11,97</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2,27</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,66</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,07</t>
+          <t>-11,25</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-6,04</t>
+          <t>-5,8</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,15; 6,61</t>
+          <t>-4,15; 9,37</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-13,8; 0,55</t>
+          <t>-5,59; 7,88</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-22,13; 0,94</t>
+          <t>-10,98; 16,99</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 9,35</t>
+          <t>-8,52; 6,31</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,91; 7,24</t>
+          <t>-14,13; 0,61</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-12,93; 13,48</t>
+          <t>-22,24; 2,74</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 5,39</t>
+          <t>-4,42; 5,53</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-7,86; 1,93</t>
+          <t>-8,04; 1,35</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-13,63; 3,58</t>
+          <t>-14,12; 3,91</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>11,93%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>3,49%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-0,12%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-4,27%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-24,37%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-45,38%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>11,93%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>3,49%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>-42,67%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-26,5%</t>
+          <t>-25,47%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-27,76; 27,89</t>
+          <t>-19,1; 60,57</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-45,36; 4,59</t>
+          <t>-26,42; 50,56</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-79,91; 4,12</t>
+          <t>-56,5; 99,62</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-19,12; 59,67</t>
+          <t>-28,38; 27,73</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-27,97; 46,27</t>
+          <t>-46,71; 2,59</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-56,17; 78,06</t>
+          <t>-78,95; 14,54</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-18,92; 26,03</t>
+          <t>-17,31; 27,47</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-32,42; 8,28</t>
+          <t>-31,64; 6,85</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-56,4; 17,3</t>
+          <t>-59,88; 17,77</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-1,38</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-0,72</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-0,92</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-2,26</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-4,31</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-4,18</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-1,38</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-0,72</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-1,25</t>
+          <t>-2,93</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-2,69</t>
+          <t>-1,96</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,25; 1,58</t>
+          <t>-4,79; 2,19</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-7,93; 0,02</t>
+          <t>-4,79; 2,68</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-10,27; 3,55</t>
+          <t>-6,58; 6,74</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 2,36</t>
+          <t>-6,21; 1,51</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 2,75</t>
+          <t>-8,2; -0,95</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-6,78; 5,75</t>
+          <t>-9,88; 5,4</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 0,52</t>
+          <t>-4,18; 0,84</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 0,34</t>
+          <t>-4,95; 0,02</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-7,78; 1,91</t>
+          <t>-6,5; 3,16</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-6,78%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-3,56%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-4,55%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-9,7%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-18,44%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-17,91%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-6,78%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-3,56%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-6,17%</t>
+          <t>-12,56%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-12,37%</t>
+          <t>-9,0%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-25,09; 7,44</t>
+          <t>-21,79; 12,28</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-31,69; -0,26</t>
+          <t>-21,19; 14,48</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-42,69; 15,6</t>
+          <t>-31,55; 34,01</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-22,08; 12,6</t>
+          <t>-24,46; 7,67</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-20,22; 14,85</t>
+          <t>-32,55; -4,29</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-31,79; 30,46</t>
+          <t>-41,72; 24,5</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-19,19; 2,61</t>
+          <t>-18,57; 3,98</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-20,92; 1,99</t>
+          <t>-21,49; 0,11</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-35,08; 9,53</t>
+          <t>-28,89; 15,63</t>
         </is>
       </c>
     </row>
